--- a/tracker-template.xlsx
+++ b/tracker-template.xlsx
@@ -252,7 +252,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -414,6 +414,9 @@
     <xf numFmtId="167" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,13 +813,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A2:B49"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="24" min="1" max="1"/>
     <col width="104" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="24.45" customHeight="1" s="25">
       <c r="B2" s="26" t="inlineStr">
         <is>
@@ -831,6 +835,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="17" customHeight="1" s="25">
       <c r="B5" s="28" t="inlineStr">
         <is>
@@ -845,6 +850,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="17" customHeight="1" s="25">
       <c r="B8" s="28" t="inlineStr">
         <is>
@@ -887,6 +893,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="17" customHeight="1" s="25">
       <c r="B15" s="28" t="inlineStr">
         <is>
@@ -936,141 +943,163 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="17" customHeight="1" s="25">
       <c r="B23" s="28" t="inlineStr">
         <is>
+          <t>If you know when your next capital call is due</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="25">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fill in Next call date, and Next call amount if you know it. Any spelling of the date works (2027, Q1 2027, March 2027) because only the year is used. Leave them blank and the tool spreads whatever is still uncalled evenly over about three years from the year after you funded, which is what it has always done. An amount with no date cannot be placed in a year, so it is ignored and the tool says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="25">
+      <c r="B25" s="28" t="inlineStr">
+        <is>
           <t>Cell colours</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="25">
-      <c r="B24" s="31" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow fill  —  Fill this in.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="25">
-      <c r="B25" s="32" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="25">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">   White  —  A formula. Leave it alone.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="25">
-      <c r="B27" s="33" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Not advice. The probability assumptions in the prompt are one investor’s and are meant to be argued with.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Deals in fund, Liquidity from, Liquidity to</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>How many underlying deals the position holds. This decides only how a VENTURE position is priced: a venture fund holding 20 or more is not priced like a single company. You do not need it for a fund that pays a coupon. Put 1 here if the position is a SINGLE COMPANY that pays a preferred return, which tells the tool to exit it on one date instead of spreading the payout.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
+          <t>How many underlying deals the position holds. This decides only how a VENTURE position is priced: a venture fund holding 20 or more is not priced like a single company. You do not need it for a fund that pays a coupon. Put 1 here if the position is a SINGLE COMPANY that pays a preferred return, which tells the tool to exit it on one date instead of spreading the payout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
           <t>Liquidity from / Liquidity to</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>The years, counted from when you funded the deal, over which the fund actually sells down and pays out. If a sponsor has said "expect distributions in years five through eight", put 5 and 8. Leave them blank and the tool assumes the back 40% of the hold. Note that a pay-out window and a fund's stated life are not the same thing: a fund can finish selling in year six and wind up in year seven.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
+          <t>The years, counted from when you funded the deal, over which the fund actually sells down and pays out. If a sponsor has said "expect distributions in years five through eight", put 5 and 8. Leave them blank and the tool assumes the back 40% of the hold. Note that a pay-out window and a fund's stated life are not the same thing: a fund can finish selling in year six and wind up in year seven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
           <t>You can leave most of this blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>The tool ships with a shared file for each of the common GC deals, carrying the sponsor, the vehicle, the structure, the preferred rate, the hold, the fees and when the GP says it pays out. If your deal name matches one of those, those columns fill themselves in and you only need YOUR numbers: commitment, funded to date, uncalled, and the year you funded it. Anything you do type wins over the shared file, always. A deal nobody has shared still works; you just supply its terms yourself.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="24" t="inlineStr">
         <is>
+          <t>The tool ships with a shared file for each of the common GC deals, carrying the sponsor, the vehicle, the structure, the preferred rate, the hold, the fees and when the GP says it pays out. If your deal name matches one of those, those columns fill themselves in and you only need YOUR numbers: commitment, funded to date, uncalled, and the year you funded it. Anything you do type wins over the shared file, always. A deal nobody has shared still works; you just supply its terms yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
           <t>Thesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>Why you did the deal, in your own words. This is yours and it is never pre-filled from anywhere, because somebody else's reasoning is not your reasoning. It shows on the deal card and never leaves your machine.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
         <is>
+          <t>Why you did the deal, in your own words. This is yours and it is never pre-filled from anywhere, because somebody else's reasoning is not your reasoning. It shows on the deal card and never leaves your machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
           <t>Fund or Single deal</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>Type "Fund" if the position holds several underlying investments, or "Single deal" if it is one company or one property. This is the simplest way to tell the tool how a position pays out: a fund sells down over several years, a single deal is bought on one date. It beats anything the tool would otherwise guess, including the Deals in fund count. If you leave it blank the tool still works out a sensible answer, but saying it outright is better.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="51" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
         <is>
           <t>NEW IN THIS VERSION</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="52" t="inlineStr">
-        <is>
-          <t>· Account, on Positions: which account each deal is held in. Leave it blank and everything still works.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="52" t="inlineStr">
-        <is>
-          <t>· You: your ages, your spend target and your benefit. Drives the Liquidity Runway tab.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="52" t="inlineStr">
         <is>
-          <t>· Balances: everything that is not a private deal, one row per account and sleeve.</t>
+          <t>· Account, on Positions: which account each deal is held in. Leave it blank and everything still works.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="52" t="inlineStr">
         <is>
-          <t>· Property, Cashflows and Events: a house sale, a pension, an inheritance, a big bill.</t>
+          <t>· You: your ages, your spend target and your benefit. Drives the Liquidity Runway tab.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="52" t="inlineStr">
+        <is>
+          <t>· Balances: everything that is not a private deal, one row per account and sleeve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="52" t="inlineStr">
+        <is>
+          <t>· Property, Cashflows and Events: a house sale, a pension, an inheritance, a big bill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="52" t="inlineStr">
         <is>
           <t>· All three are optional. A tracker without them behaves exactly as it did before.</t>
         </is>
@@ -1089,7 +1118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="24" min="1" max="1"/>
@@ -1109,12 +1138,14 @@
     <col width="46" customWidth="1" style="25" min="19" max="19"/>
     <col width="18" customWidth="1" style="25" min="20" max="20"/>
     <col width="15" customWidth="1" style="25" min="21" max="21"/>
+    <col width="18" customWidth="1" style="25" min="23" max="23"/>
+    <col width="18" customWidth="1" style="25" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="25">
       <c r="A1" s="34" t="inlineStr">
         <is>
-          <t>Positions  ·  fill in the yellow cells, one row per deal        TRACKER v1.7</t>
+          <t>Positions  ·  fill in the yellow cells, one row per deal        TRACKER v1.8</t>
         </is>
       </c>
     </row>
@@ -1227,6 +1258,16 @@
       <c r="V2" s="36" t="inlineStr">
         <is>
           <t>Marked Up MOIC</t>
+        </is>
+      </c>
+      <c r="W2" s="36" t="inlineStr">
+        <is>
+          <t>Next call date</t>
+        </is>
+      </c>
+      <c r="X2" s="36" t="inlineStr">
+        <is>
+          <t>Next call amount</t>
         </is>
       </c>
     </row>
@@ -1291,6 +1332,8 @@
       </c>
       <c r="U3" s="37" t="n"/>
       <c r="V3" s="42" t="n"/>
+      <c r="W3" s="59" t="n"/>
+      <c r="X3" s="37" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="37" t="inlineStr">
@@ -1349,6 +1392,8 @@
       <c r="T4" s="37" t="n"/>
       <c r="U4" s="37" t="n"/>
       <c r="V4" s="42" t="n"/>
+      <c r="W4" s="59" t="n"/>
+      <c r="X4" s="37" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="25">
       <c r="A5" s="37" t="inlineStr">
@@ -1407,6 +1452,8 @@
       <c r="T5" s="37" t="n"/>
       <c r="U5" s="37" t="n"/>
       <c r="V5" s="42" t="n"/>
+      <c r="W5" s="59" t="n"/>
+      <c r="X5" s="37" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="25">
       <c r="A6" s="37" t="inlineStr">
@@ -1460,6 +1507,8 @@
       <c r="T6" s="37" t="n"/>
       <c r="U6" s="37" t="n"/>
       <c r="V6" s="42" t="n"/>
+      <c r="W6" s="59" t="n"/>
+      <c r="X6" s="37" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="25">
       <c r="A7" s="37" t="inlineStr">
@@ -1517,6 +1566,12 @@
       </c>
       <c r="U7" s="37" t="n"/>
       <c r="V7" s="42" t="n"/>
+      <c r="W7" s="59" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="X7" s="37" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="25">
       <c r="A8" s="37" t="inlineStr">
@@ -1574,6 +1629,8 @@
       </c>
       <c r="U8" s="37" t="n"/>
       <c r="V8" s="42" t="n"/>
+      <c r="W8" s="59" t="n"/>
+      <c r="X8" s="37" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="25">
       <c r="A9" s="37" t="inlineStr">
@@ -1627,6 +1684,8 @@
       <c r="T9" s="37" t="n"/>
       <c r="U9" s="37" t="n"/>
       <c r="V9" s="42" t="n"/>
+      <c r="W9" s="59" t="n"/>
+      <c r="X9" s="37" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="25">
       <c r="A10" s="37" t="inlineStr">
@@ -1680,6 +1739,8 @@
       <c r="T10" s="37" t="n"/>
       <c r="U10" s="37" t="n"/>
       <c r="V10" s="42" t="n"/>
+      <c r="W10" s="59" t="n"/>
+      <c r="X10" s="37" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="25">
       <c r="A11" s="37" t="inlineStr">
@@ -1733,6 +1794,8 @@
       <c r="T11" s="37" t="n"/>
       <c r="U11" s="37" t="n"/>
       <c r="V11" s="42" t="n"/>
+      <c r="W11" s="59" t="n"/>
+      <c r="X11" s="37" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="25">
       <c r="A12" s="37" t="inlineStr">
@@ -1786,6 +1849,8 @@
       <c r="T12" s="37" t="n"/>
       <c r="U12" s="37" t="n"/>
       <c r="V12" s="42" t="n"/>
+      <c r="W12" s="59" t="n"/>
+      <c r="X12" s="37" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="25">
       <c r="A13" s="37" t="inlineStr">
@@ -1839,6 +1904,8 @@
       <c r="T13" s="37" t="n"/>
       <c r="U13" s="37" t="n"/>
       <c r="V13" s="42" t="n"/>
+      <c r="W13" s="59" t="n"/>
+      <c r="X13" s="37" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="25">
       <c r="A14" s="37" t="inlineStr">
@@ -1892,6 +1959,8 @@
       <c r="T14" s="37" t="n"/>
       <c r="U14" s="37" t="n"/>
       <c r="V14" s="42" t="n"/>
+      <c r="W14" s="59" t="n"/>
+      <c r="X14" s="37" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="25">
       <c r="A15" s="37" t="inlineStr">
@@ -1945,6 +2014,8 @@
       <c r="T15" s="37" t="n"/>
       <c r="U15" s="37" t="n"/>
       <c r="V15" s="42" t="n"/>
+      <c r="W15" s="59" t="n"/>
+      <c r="X15" s="37" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="25">
       <c r="A16" s="46" t="inlineStr">
@@ -1973,8 +2044,13 @@
           <t>Single deal</t>
         </is>
       </c>
-    </row>
-    <row r="17"/>
+      <c r="W16" s="59" t="n"/>
+      <c r="X16" s="37" t="n"/>
+    </row>
+    <row r="17">
+      <c r="W17" s="59" t="n"/>
+      <c r="X17" s="37" t="n"/>
+    </row>
     <row r="18" ht="15" customHeight="1" s="25">
       <c r="A18" s="48" t="inlineStr">
         <is>
@@ -1992,6 +2068,8 @@
           <t>Single deal</t>
         </is>
       </c>
+      <c r="W18" s="59" t="n"/>
+      <c r="X18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
@@ -1999,6 +2077,8 @@
           <t>Hold, Coupon, Sponsor MOIC, Asset class and the fund columns are deliberately BLANK on these example rows. Those terms are identical for everyone who bought the deal, so they now live in one shared file per deal and the tool fills them in. Anything you type here overrides the shared file and nothing argues with you — which is why a figure typed before a sponsor corrected its terms is worth checking.</t>
         </is>
       </c>
+      <c r="W19" s="59" t="n"/>
+      <c r="X19" s="37" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="25">
       <c r="A20" s="48" t="inlineStr">
@@ -2017,6 +2097,8 @@
           <t>Single deal</t>
         </is>
       </c>
+      <c r="W20" s="59" t="n"/>
+      <c r="X20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
@@ -2024,6 +2106,8 @@
           <t>Marked Up MOIC is optional. It records what you believe a position is worth now, and it drives a paper track shown beside the cash forecast rather than inside it. It never moves a cash figure and never enters the IRR.</t>
         </is>
       </c>
+      <c r="W21" s="59" t="n"/>
+      <c r="X21" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tracker-template.xlsx
+++ b/tracker-template.xlsx
@@ -404,6 +404,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -414,9 +417,6 @@
     <xf numFmtId="167" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,14 +813,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A2:B51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="24" min="1" max="1"/>
     <col width="104" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="24.45" customHeight="1" s="25">
       <c r="B2" s="26" t="inlineStr">
         <is>
@@ -835,7 +834,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="17" customHeight="1" s="25">
       <c r="B5" s="28" t="inlineStr">
         <is>
@@ -850,7 +848,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="17" customHeight="1" s="25">
       <c r="B8" s="28" t="inlineStr">
         <is>
@@ -893,7 +890,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="17" customHeight="1" s="25">
       <c r="B15" s="28" t="inlineStr">
         <is>
@@ -943,7 +939,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="17" customHeight="1" s="25">
       <c r="B23" s="28" t="inlineStr">
         <is>
@@ -952,7 +947,7 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="25">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Fill in Next call date, and Next call amount if you know it. Any spelling of the date works (2027, Q1 2027, March 2027) because only the year is used. Leave them blank and the tool spreads whatever is still uncalled evenly over about three years from the year after you funded, which is what it has always done. An amount with no date cannot be placed in a year, so it is ignored and the tool says so.</t>
         </is>
@@ -979,7 +974,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="B29" s="33" t="inlineStr">
         <is>
@@ -987,7 +981,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
@@ -1002,7 +995,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
@@ -1017,7 +1009,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
@@ -1032,7 +1023,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
@@ -1047,7 +1037,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
@@ -1062,44 +1051,43 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
-      <c r="A46" s="51" t="inlineStr">
+      <c r="A46" s="52" t="inlineStr">
         <is>
           <t>NEW IN THIS VERSION</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="52" t="inlineStr">
+      <c r="A47" s="53" t="inlineStr">
         <is>
           <t>· Account, on Positions: which account each deal is held in. Leave it blank and everything still works.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="52" t="inlineStr">
+      <c r="A48" s="53" t="inlineStr">
         <is>
           <t>· You: your ages, your spend target and your benefit. Drives the Liquidity Runway tab.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="A49" s="53" t="inlineStr">
         <is>
           <t>· Balances: everything that is not a private deal, one row per account and sleeve.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="52" t="inlineStr">
+      <c r="A50" s="53" t="inlineStr">
         <is>
           <t>· Property, Cashflows and Events: a house sale, a pension, an inheritance, a big bill.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="52" t="inlineStr">
+      <c r="A51" s="53" t="inlineStr">
         <is>
           <t>· All three are optional. A tracker without them behaves exactly as it did before.</t>
         </is>
@@ -1121,23 +1109,24 @@
   <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="24" min="1" max="1"/>
-    <col width="22" customWidth="1" style="24" min="2" max="2"/>
-    <col width="16" customWidth="1" style="24" min="3" max="3"/>
-    <col width="14" customWidth="1" style="24" min="4" max="5"/>
-    <col width="13" customWidth="1" style="24" min="6" max="6"/>
-    <col width="12" customWidth="1" style="24" min="7" max="7"/>
-    <col width="11" customWidth="1" style="24" min="8" max="9"/>
-    <col width="13" customWidth="1" style="24" min="10" max="10"/>
-    <col width="12" customWidth="1" style="24" min="11" max="11"/>
-    <col width="13" customWidth="1" style="24" min="12" max="14"/>
-    <col width="14" customWidth="1" style="24" min="15" max="15"/>
-    <col width="13" customWidth="1" style="25" min="16" max="16"/>
-    <col width="14" customWidth="1" style="25" min="17" max="17"/>
+    <col width="30" customWidth="1" style="25" min="1" max="1"/>
+    <col width="22" customWidth="1" style="25" min="2" max="2"/>
+    <col width="11" customWidth="1" style="25" min="3" max="3"/>
+    <col width="16" customWidth="1" style="25" min="4" max="4"/>
+    <col width="14" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="12" customWidth="1" style="25" min="8" max="8"/>
+    <col width="11" customWidth="1" style="25" min="9" max="9"/>
+    <col width="13" customWidth="1" style="25" min="11" max="11"/>
+    <col width="12" customWidth="1" style="25" min="12" max="12"/>
+    <col width="13" customWidth="1" style="25" min="13" max="13"/>
+    <col width="14" customWidth="1" style="25" min="16" max="16"/>
+    <col width="13" customWidth="1" style="25" min="17" max="17"/>
     <col width="14" customWidth="1" style="25" min="18" max="18"/>
-    <col width="46" customWidth="1" style="25" min="19" max="19"/>
-    <col width="18" customWidth="1" style="25" min="20" max="20"/>
-    <col width="15" customWidth="1" style="25" min="21" max="21"/>
+    <col width="14" customWidth="1" style="25" min="19" max="19"/>
+    <col width="46" customWidth="1" style="25" min="20" max="20"/>
+    <col width="18" customWidth="1" style="25" min="21" max="21"/>
+    <col width="15" customWidth="1" style="25" min="22" max="22"/>
     <col width="18" customWidth="1" style="25" min="23" max="23"/>
     <col width="18" customWidth="1" style="25" min="24" max="24"/>
   </cols>
@@ -1277,7 +1266,7 @@
           <t>Eephus Growth Fund I</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="54" t="inlineStr">
         <is>
           <t>Equity Trust SDIRA</t>
         </is>
@@ -1295,7 +1284,7 @@
         <v>50000</v>
       </c>
       <c r="G3" s="39">
-        <f>MAX(0,D3-E3)</f>
+        <f>MAX(0,E3-F3)</f>
         <v/>
       </c>
       <c r="H3" s="45" t="n">
@@ -1310,15 +1299,15 @@
         </is>
       </c>
       <c r="M3" s="43">
-        <f>IF(M3="","",M3-MIN(3,MAX(1,ROUND(H3*0.3,0))))</f>
+        <f>IF(N3="","",N3-MIN(3,MAX(1,ROUND(I3*0.3,0))))</f>
         <v/>
       </c>
       <c r="N3" s="43">
-        <f>IF(O3&lt;&gt;"",O3,IF(H3="","",G3+H3))</f>
+        <f>IF(P3&lt;&gt;"",P3,IF(I3="","",H3+I3))</f>
         <v/>
       </c>
       <c r="O3" s="43">
-        <f>IF(M3="","",M3+2)</f>
+        <f>IF(N3="","",N3+2)</f>
         <v/>
       </c>
       <c r="P3" s="44" t="n"/>
@@ -1332,8 +1321,8 @@
       </c>
       <c r="U3" s="37" t="n"/>
       <c r="V3" s="42" t="n"/>
-      <c r="W3" s="59" t="n"/>
-      <c r="X3" s="37" t="n"/>
+      <c r="W3" s="51" t="n"/>
+      <c r="X3" s="38" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="37" t="inlineStr">
@@ -1341,7 +1330,7 @@
           <t>Eephus Growth Fund II</t>
         </is>
       </c>
-      <c r="B4" s="53" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
         <is>
           <t>Equity Trust SDIRA</t>
         </is>
@@ -1359,7 +1348,7 @@
         <v>50000</v>
       </c>
       <c r="G4" s="39">
-        <f>MAX(0,D4-E4)</f>
+        <f>MAX(0,E4-F4)</f>
         <v/>
       </c>
       <c r="H4" s="45" t="n">
@@ -1374,15 +1363,15 @@
         </is>
       </c>
       <c r="M4" s="43">
-        <f>IF(M4="","",M4-MIN(3,MAX(1,ROUND(H4*0.3,0))))</f>
+        <f>IF(N4="","",N4-MIN(3,MAX(1,ROUND(I4*0.3,0))))</f>
         <v/>
       </c>
       <c r="N4" s="43">
-        <f>IF(O4&lt;&gt;"",O4,IF(H4="","",G4+H4))</f>
+        <f>IF(P4&lt;&gt;"",P4,IF(I4="","",H4+I4))</f>
         <v/>
       </c>
       <c r="O4" s="43">
-        <f>IF(M4="","",M4+2)</f>
+        <f>IF(N4="","",N4+2)</f>
         <v/>
       </c>
       <c r="P4" s="44" t="n"/>
@@ -1392,8 +1381,8 @@
       <c r="T4" s="37" t="n"/>
       <c r="U4" s="37" t="n"/>
       <c r="V4" s="42" t="n"/>
-      <c r="W4" s="59" t="n"/>
-      <c r="X4" s="37" t="n"/>
+      <c r="W4" s="51" t="n"/>
+      <c r="X4" s="38" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="25">
       <c r="A5" s="37" t="inlineStr">
@@ -1401,7 +1390,7 @@
           <t>BlueBird Capital (Tranche 1)</t>
         </is>
       </c>
-      <c r="B5" s="53" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>Equity Trust SDIRA</t>
         </is>
@@ -1419,7 +1408,7 @@
         <v>50000</v>
       </c>
       <c r="G5" s="39">
-        <f>MAX(0,D5-E5)</f>
+        <f>MAX(0,E5-F5)</f>
         <v/>
       </c>
       <c r="H5" s="45" t="n">
@@ -1434,15 +1423,15 @@
         </is>
       </c>
       <c r="M5" s="43">
-        <f>IF(M5="","",M5-MIN(3,MAX(1,ROUND(H5*0.3,0))))</f>
+        <f>IF(N5="","",N5-MIN(3,MAX(1,ROUND(I5*0.3,0))))</f>
         <v/>
       </c>
       <c r="N5" s="43">
-        <f>IF(O5&lt;&gt;"",O5,IF(H5="","",G5+H5))</f>
+        <f>IF(P5&lt;&gt;"",P5,IF(I5="","",H5+I5))</f>
         <v/>
       </c>
       <c r="O5" s="43">
-        <f>IF(M5="","",M5+2)</f>
+        <f>IF(N5="","",N5+2)</f>
         <v/>
       </c>
       <c r="P5" s="44" t="n"/>
@@ -1452,8 +1441,8 @@
       <c r="T5" s="37" t="n"/>
       <c r="U5" s="37" t="n"/>
       <c r="V5" s="42" t="n"/>
-      <c r="W5" s="59" t="n"/>
-      <c r="X5" s="37" t="n"/>
+      <c r="W5" s="51" t="n"/>
+      <c r="X5" s="38" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="25">
       <c r="A6" s="37" t="inlineStr">
@@ -1474,7 +1463,7 @@
         <v>50000</v>
       </c>
       <c r="G6" s="39">
-        <f>MAX(0,D6-E6)</f>
+        <f>MAX(0,E6-F6)</f>
         <v/>
       </c>
       <c r="H6" s="45" t="n">
@@ -1489,15 +1478,15 @@
         </is>
       </c>
       <c r="M6" s="43">
-        <f>IF(M6="","",M6-MIN(3,MAX(1,ROUND(H6*0.3,0))))</f>
+        <f>IF(N6="","",N6-MIN(3,MAX(1,ROUND(I6*0.3,0))))</f>
         <v/>
       </c>
       <c r="N6" s="43">
-        <f>IF(O6&lt;&gt;"",O6,IF(H6="","",G6+H6))</f>
+        <f>IF(P6&lt;&gt;"",P6,IF(I6="","",H6+I6))</f>
         <v/>
       </c>
       <c r="O6" s="43">
-        <f>IF(M6="","",M6+2)</f>
+        <f>IF(N6="","",N6+2)</f>
         <v/>
       </c>
       <c r="P6" s="44" t="n"/>
@@ -1507,8 +1496,8 @@
       <c r="T6" s="37" t="n"/>
       <c r="U6" s="37" t="n"/>
       <c r="V6" s="42" t="n"/>
-      <c r="W6" s="59" t="n"/>
-      <c r="X6" s="37" t="n"/>
+      <c r="W6" s="51" t="n"/>
+      <c r="X6" s="38" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="25">
       <c r="A7" s="37" t="inlineStr">
@@ -1526,10 +1515,10 @@
         <v>100000</v>
       </c>
       <c r="F7" s="38" t="n">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="G7" s="39">
-        <f>MAX(0,D7-E7)</f>
+        <f>MAX(0,E7-F7)</f>
         <v/>
       </c>
       <c r="H7" s="45" t="n">
@@ -1544,15 +1533,15 @@
         </is>
       </c>
       <c r="M7" s="43">
-        <f>IF(M7="","",M7-MIN(3,MAX(1,ROUND(H7*0.3,0))))</f>
+        <f>IF(N7="","",N7-MIN(3,MAX(1,ROUND(I7*0.3,0))))</f>
         <v/>
       </c>
       <c r="N7" s="43">
-        <f>IF(O7&lt;&gt;"",O7,IF(H7="","",G7+H7))</f>
+        <f>IF(P7&lt;&gt;"",P7,IF(I7="","",H7+I7))</f>
         <v/>
       </c>
       <c r="O7" s="43">
-        <f>IF(M7="","",M7+2)</f>
+        <f>IF(N7="","",N7+2)</f>
         <v/>
       </c>
       <c r="P7" s="44" t="n"/>
@@ -1566,12 +1555,12 @@
       </c>
       <c r="U7" s="37" t="n"/>
       <c r="V7" s="42" t="n"/>
-      <c r="W7" s="59" t="inlineStr">
+      <c r="W7" s="51" t="inlineStr">
         <is>
           <t>Q1 2027</t>
         </is>
       </c>
-      <c r="X7" s="37" t="n"/>
+      <c r="X7" s="38" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="25">
       <c r="A8" s="37" t="inlineStr">
@@ -1592,7 +1581,7 @@
         <v>75000</v>
       </c>
       <c r="G8" s="39">
-        <f>MAX(0,D8-E8)</f>
+        <f>MAX(0,E8-F8)</f>
         <v/>
       </c>
       <c r="H8" s="45" t="n">
@@ -1607,15 +1596,15 @@
         </is>
       </c>
       <c r="M8" s="43">
-        <f>IF(M8="","",M8-MIN(3,MAX(1,ROUND(H8*0.3,0))))</f>
+        <f>IF(N8="","",N8-MIN(3,MAX(1,ROUND(I8*0.3,0))))</f>
         <v/>
       </c>
       <c r="N8" s="43">
-        <f>IF(O8&lt;&gt;"",O8,IF(H8="","",G8+H8))</f>
+        <f>IF(P8&lt;&gt;"",P8,IF(I8="","",H8+I8))</f>
         <v/>
       </c>
       <c r="O8" s="43">
-        <f>IF(M8="","",M8+2)</f>
+        <f>IF(N8="","",N8+2)</f>
         <v/>
       </c>
       <c r="P8" s="44" t="n"/>
@@ -1629,8 +1618,8 @@
       </c>
       <c r="U8" s="37" t="n"/>
       <c r="V8" s="42" t="n"/>
-      <c r="W8" s="59" t="n"/>
-      <c r="X8" s="37" t="n"/>
+      <c r="W8" s="51" t="n"/>
+      <c r="X8" s="38" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="25">
       <c r="A9" s="37" t="inlineStr">
@@ -1651,7 +1640,7 @@
         <v>25000</v>
       </c>
       <c r="G9" s="39">
-        <f>MAX(0,D9-E9)</f>
+        <f>MAX(0,E9-F9)</f>
         <v/>
       </c>
       <c r="H9" s="45" t="n">
@@ -1666,15 +1655,15 @@
         </is>
       </c>
       <c r="M9" s="43">
-        <f>IF(M9="","",M9-MIN(3,MAX(1,ROUND(H9*0.3,0))))</f>
+        <f>IF(N9="","",N9-MIN(3,MAX(1,ROUND(I9*0.3,0))))</f>
         <v/>
       </c>
       <c r="N9" s="43">
-        <f>IF(O9&lt;&gt;"",O9,IF(H9="","",G9+H9))</f>
+        <f>IF(P9&lt;&gt;"",P9,IF(I9="","",H9+I9))</f>
         <v/>
       </c>
       <c r="O9" s="43">
-        <f>IF(M9="","",M9+2)</f>
+        <f>IF(N9="","",N9+2)</f>
         <v/>
       </c>
       <c r="P9" s="44" t="n"/>
@@ -1684,8 +1673,8 @@
       <c r="T9" s="37" t="n"/>
       <c r="U9" s="37" t="n"/>
       <c r="V9" s="42" t="n"/>
-      <c r="W9" s="59" t="n"/>
-      <c r="X9" s="37" t="n"/>
+      <c r="W9" s="51" t="n"/>
+      <c r="X9" s="38" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="25">
       <c r="A10" s="37" t="inlineStr">
@@ -1706,7 +1695,7 @@
         <v>25000</v>
       </c>
       <c r="G10" s="39">
-        <f>MAX(0,D10-E10)</f>
+        <f>MAX(0,E10-F10)</f>
         <v/>
       </c>
       <c r="H10" s="45" t="n">
@@ -1721,15 +1710,15 @@
         </is>
       </c>
       <c r="M10" s="43">
-        <f>IF(M10="","",M10-MIN(3,MAX(1,ROUND(H10*0.3,0))))</f>
+        <f>IF(N10="","",N10-MIN(3,MAX(1,ROUND(I10*0.3,0))))</f>
         <v/>
       </c>
       <c r="N10" s="43">
-        <f>IF(O10&lt;&gt;"",O10,IF(H10="","",G10+H10))</f>
+        <f>IF(P10&lt;&gt;"",P10,IF(I10="","",H10+I10))</f>
         <v/>
       </c>
       <c r="O10" s="43">
-        <f>IF(M10="","",M10+2)</f>
+        <f>IF(N10="","",N10+2)</f>
         <v/>
       </c>
       <c r="P10" s="44" t="n"/>
@@ -1739,8 +1728,8 @@
       <c r="T10" s="37" t="n"/>
       <c r="U10" s="37" t="n"/>
       <c r="V10" s="42" t="n"/>
-      <c r="W10" s="59" t="n"/>
-      <c r="X10" s="37" t="n"/>
+      <c r="W10" s="51" t="n"/>
+      <c r="X10" s="38" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="25">
       <c r="A11" s="37" t="inlineStr">
@@ -1761,7 +1750,7 @@
         <v>20000</v>
       </c>
       <c r="G11" s="39">
-        <f>MAX(0,D11-E11)</f>
+        <f>MAX(0,E11-F11)</f>
         <v/>
       </c>
       <c r="H11" s="45" t="n">
@@ -1776,15 +1765,15 @@
         </is>
       </c>
       <c r="M11" s="43">
-        <f>IF(M11="","",M11-MIN(3,MAX(1,ROUND(H11*0.3,0))))</f>
+        <f>IF(N11="","",N11-MIN(3,MAX(1,ROUND(I11*0.3,0))))</f>
         <v/>
       </c>
       <c r="N11" s="43">
-        <f>IF(O11&lt;&gt;"",O11,IF(H11="","",G11+H11))</f>
+        <f>IF(P11&lt;&gt;"",P11,IF(I11="","",H11+I11))</f>
         <v/>
       </c>
       <c r="O11" s="43">
-        <f>IF(M11="","",M11+2)</f>
+        <f>IF(N11="","",N11+2)</f>
         <v/>
       </c>
       <c r="P11" s="44" t="n"/>
@@ -1794,8 +1783,8 @@
       <c r="T11" s="37" t="n"/>
       <c r="U11" s="37" t="n"/>
       <c r="V11" s="42" t="n"/>
-      <c r="W11" s="59" t="n"/>
-      <c r="X11" s="37" t="n"/>
+      <c r="W11" s="51" t="n"/>
+      <c r="X11" s="38" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="25">
       <c r="A12" s="37" t="inlineStr">
@@ -1816,7 +1805,7 @@
         <v>20000</v>
       </c>
       <c r="G12" s="39">
-        <f>MAX(0,D12-E12)</f>
+        <f>MAX(0,E12-F12)</f>
         <v/>
       </c>
       <c r="H12" s="45" t="n">
@@ -1831,15 +1820,15 @@
         </is>
       </c>
       <c r="M12" s="43">
-        <f>IF(M12="","",M12-MIN(3,MAX(1,ROUND(H12*0.3,0))))</f>
+        <f>IF(N12="","",N12-MIN(3,MAX(1,ROUND(I12*0.3,0))))</f>
         <v/>
       </c>
       <c r="N12" s="43">
-        <f>IF(O12&lt;&gt;"",O12,IF(H12="","",G12+H12))</f>
+        <f>IF(P12&lt;&gt;"",P12,IF(I12="","",H12+I12))</f>
         <v/>
       </c>
       <c r="O12" s="43">
-        <f>IF(M12="","",M12+2)</f>
+        <f>IF(N12="","",N12+2)</f>
         <v/>
       </c>
       <c r="P12" s="44" t="n"/>
@@ -1849,8 +1838,8 @@
       <c r="T12" s="37" t="n"/>
       <c r="U12" s="37" t="n"/>
       <c r="V12" s="42" t="n"/>
-      <c r="W12" s="59" t="n"/>
-      <c r="X12" s="37" t="n"/>
+      <c r="W12" s="51" t="n"/>
+      <c r="X12" s="38" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="25">
       <c r="A13" s="37" t="inlineStr">
@@ -1871,7 +1860,7 @@
         <v>10000</v>
       </c>
       <c r="G13" s="39">
-        <f>MAX(0,D13-E13)</f>
+        <f>MAX(0,E13-F13)</f>
         <v/>
       </c>
       <c r="H13" s="45" t="n">
@@ -1886,15 +1875,15 @@
         </is>
       </c>
       <c r="M13" s="43">
-        <f>IF(M13="","",M13-MIN(3,MAX(1,ROUND(H13*0.3,0))))</f>
+        <f>IF(N13="","",N13-MIN(3,MAX(1,ROUND(I13*0.3,0))))</f>
         <v/>
       </c>
       <c r="N13" s="43">
-        <f>IF(O13&lt;&gt;"",O13,IF(H13="","",G13+H13))</f>
+        <f>IF(P13&lt;&gt;"",P13,IF(I13="","",H13+I13))</f>
         <v/>
       </c>
       <c r="O13" s="43">
-        <f>IF(M13="","",M13+2)</f>
+        <f>IF(N13="","",N13+2)</f>
         <v/>
       </c>
       <c r="P13" s="44" t="n"/>
@@ -1904,8 +1893,8 @@
       <c r="T13" s="37" t="n"/>
       <c r="U13" s="37" t="n"/>
       <c r="V13" s="42" t="n"/>
-      <c r="W13" s="59" t="n"/>
-      <c r="X13" s="37" t="n"/>
+      <c r="W13" s="51" t="n"/>
+      <c r="X13" s="38" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="25">
       <c r="A14" s="37" t="inlineStr">
@@ -1926,7 +1915,7 @@
         <v>10000</v>
       </c>
       <c r="G14" s="39">
-        <f>MAX(0,D14-E14)</f>
+        <f>MAX(0,E14-F14)</f>
         <v/>
       </c>
       <c r="H14" s="45" t="n">
@@ -1941,15 +1930,15 @@
         </is>
       </c>
       <c r="M14" s="43">
-        <f>IF(M14="","",M14-MIN(3,MAX(1,ROUND(H14*0.3,0))))</f>
+        <f>IF(N14="","",N14-MIN(3,MAX(1,ROUND(I14*0.3,0))))</f>
         <v/>
       </c>
       <c r="N14" s="43">
-        <f>IF(O14&lt;&gt;"",O14,IF(H14="","",G14+H14))</f>
+        <f>IF(P14&lt;&gt;"",P14,IF(I14="","",H14+I14))</f>
         <v/>
       </c>
       <c r="O14" s="43">
-        <f>IF(M14="","",M14+2)</f>
+        <f>IF(N14="","",N14+2)</f>
         <v/>
       </c>
       <c r="P14" s="44" t="n"/>
@@ -1959,8 +1948,8 @@
       <c r="T14" s="37" t="n"/>
       <c r="U14" s="37" t="n"/>
       <c r="V14" s="42" t="n"/>
-      <c r="W14" s="59" t="n"/>
-      <c r="X14" s="37" t="n"/>
+      <c r="W14" s="51" t="n"/>
+      <c r="X14" s="38" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="25">
       <c r="A15" s="37" t="inlineStr">
@@ -1981,7 +1970,7 @@
         <v>5000</v>
       </c>
       <c r="G15" s="39">
-        <f>MAX(0,D15-E15)</f>
+        <f>MAX(0,E15-F15)</f>
         <v/>
       </c>
       <c r="H15" s="45" t="n">
@@ -1996,15 +1985,15 @@
         </is>
       </c>
       <c r="M15" s="43">
-        <f>IF(M15="","",M15-MIN(3,MAX(1,ROUND(H15*0.3,0))))</f>
+        <f>IF(N15="","",N15-MIN(3,MAX(1,ROUND(I15*0.3,0))))</f>
         <v/>
       </c>
       <c r="N15" s="43">
-        <f>IF(O15&lt;&gt;"",O15,IF(H15="","",G15+H15))</f>
+        <f>IF(P15&lt;&gt;"",P15,IF(I15="","",H15+I15))</f>
         <v/>
       </c>
       <c r="O15" s="43">
-        <f>IF(M15="","",M15+2)</f>
+        <f>IF(N15="","",N15+2)</f>
         <v/>
       </c>
       <c r="P15" s="44" t="n"/>
@@ -2014,8 +2003,8 @@
       <c r="T15" s="37" t="n"/>
       <c r="U15" s="37" t="n"/>
       <c r="V15" s="42" t="n"/>
-      <c r="W15" s="59" t="n"/>
-      <c r="X15" s="37" t="n"/>
+      <c r="W15" s="51" t="n"/>
+      <c r="X15" s="38" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="25">
       <c r="A16" s="46" t="inlineStr">
@@ -2024,15 +2013,15 @@
         </is>
       </c>
       <c r="E16" s="47">
-        <f>SUM(D3:D15)</f>
+        <f>SUM(E3:E15)</f>
         <v/>
       </c>
       <c r="F16" s="47">
-        <f>SUM(E3:E15)</f>
+        <f>SUM(F3:F15)</f>
         <v/>
       </c>
       <c r="G16" s="47">
-        <f>SUM(F3:F15)</f>
+        <f>SUM(G3:G15)</f>
         <v/>
       </c>
       <c r="Q16" s="45" t="n"/>
@@ -2044,17 +2033,17 @@
           <t>Single deal</t>
         </is>
       </c>
-      <c r="W16" s="59" t="n"/>
-      <c r="X16" s="37" t="n"/>
+      <c r="W16" s="51" t="n"/>
+      <c r="X16" s="38" t="n"/>
     </row>
     <row r="17">
-      <c r="W17" s="59" t="n"/>
-      <c r="X17" s="37" t="n"/>
+      <c r="W17" s="51" t="n"/>
+      <c r="X17" s="38" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="25">
       <c r="A18" s="48" t="inlineStr">
         <is>
-          <t>Blue text is something you typed. Black is a formula. Column F and the three exit-year columns work themselves out; put a year in Override likely only if you know better than the derived one.</t>
+          <t>Blue text is something you typed. Black is a formula. Column G and the three exit-year columns work themselves out; put a year in Override likely only if you know better than the derived one.</t>
         </is>
       </c>
       <c r="Q18" s="45" t="n">
@@ -2068,8 +2057,8 @@
           <t>Single deal</t>
         </is>
       </c>
-      <c r="W18" s="59" t="n"/>
-      <c r="X18" s="37" t="n"/>
+      <c r="W18" s="51" t="n"/>
+      <c r="X18" s="38" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
@@ -2077,8 +2066,8 @@
           <t>Hold, Coupon, Sponsor MOIC, Asset class and the fund columns are deliberately BLANK on these example rows. Those terms are identical for everyone who bought the deal, so they now live in one shared file per deal and the tool fills them in. Anything you type here overrides the shared file and nothing argues with you — which is why a figure typed before a sponsor corrected its terms is worth checking.</t>
         </is>
       </c>
-      <c r="W19" s="59" t="n"/>
-      <c r="X19" s="37" t="n"/>
+      <c r="W19" s="51" t="n"/>
+      <c r="X19" s="38" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="25">
       <c r="A20" s="48" t="inlineStr">
@@ -2097,8 +2086,8 @@
           <t>Single deal</t>
         </is>
       </c>
-      <c r="W20" s="59" t="n"/>
-      <c r="X20" s="37" t="n"/>
+      <c r="W20" s="51" t="n"/>
+      <c r="X20" s="38" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
@@ -2106,13 +2095,13 @@
           <t>Marked Up MOIC is optional. It records what you believe a position is worth now, and it drives a paper track shown beside the cash forecast rather than inside it. It never moves a cash figure and never enters the IRR.</t>
         </is>
       </c>
-      <c r="W21" s="59" t="n"/>
-      <c r="X21" s="37" t="n"/>
+      <c r="W21" s="51" t="n"/>
+      <c r="X21" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A18:L18"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2240,162 +2229,162 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>You  ·  the plan these numbers are for</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B2" s="54" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Your number</t>
         </is>
       </c>
-      <c r="C2" s="54" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>What it means</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>Birth year</t>
         </is>
       </c>
-      <c r="B3" s="53" t="n">
+      <c r="B3" s="54" t="n">
         <v>1975</v>
       </c>
-      <c r="C3" s="55" t="inlineStr">
+      <c r="C3" s="56" t="inlineStr">
         <is>
           <t>Ages are worked out from this, so the sheet does not go stale each birthday.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>Planned stop work year</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n">
+      <c r="B4" s="54" t="n">
         <v>2040</v>
       </c>
-      <c r="C4" s="55" t="inlineStr">
+      <c r="C4" s="56" t="inlineStr">
         <is>
           <t>The app can move this without you editing the sheet.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>Plan to age</t>
         </is>
       </c>
-      <c r="B5" s="53" t="n">
+      <c r="B5" s="54" t="n">
         <v>92</v>
       </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="C5" s="56" t="inlineStr">
         <is>
           <t>How far out to model. Not a prediction about anybody.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>Annual spend target</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>180000</v>
       </c>
-      <c r="C6" s="55" t="inlineStr">
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>Today's money. What a good year looks like.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Floor spend (must-have)</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>120000</v>
       </c>
-      <c r="C7" s="55" t="inlineStr">
+      <c r="C7" s="56" t="inlineStr">
         <is>
           <t>Today's money. What you will not go below.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>Inflation until stop</t>
         </is>
       </c>
-      <c r="B8" s="57" t="n">
+      <c r="B8" s="58" t="n">
         <v>0.035</v>
       </c>
-      <c r="C8" s="55" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>Type 3.5% or 0.035, either reads the same.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>Inflation after stop</t>
         </is>
       </c>
-      <c r="B9" s="57" t="n">
+      <c r="B9" s="58" t="n">
         <v>0.03</v>
       </c>
-      <c r="C9" s="55" t="inlineStr"/>
+      <c r="C9" s="56" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="52" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>Benefit start age</t>
         </is>
       </c>
-      <c r="B10" s="53" t="n">
+      <c r="B10" s="54" t="n">
         <v>67</v>
       </c>
-      <c r="C10" s="55" t="inlineStr">
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>Social Security, a state pension, whatever applies.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>Estimated annual benefit</t>
         </is>
       </c>
-      <c r="B11" s="56" t="n">
+      <c r="B11" s="57" t="n">
         <v>40000</v>
       </c>
-      <c r="C11" s="55" t="inlineStr">
+      <c r="C11" s="56" t="inlineStr">
         <is>
           <t>Today's money, at the age above.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>Leave anything blank and the app uses its own assumption, and says on screen that it did.</t>
         </is>
@@ -2428,252 +2417,252 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Balances  ·  everything that is not itemised on Positions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B2" s="54" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Account type</t>
         </is>
       </c>
-      <c r="C2" s="54" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>Sleeve</t>
         </is>
       </c>
-      <c r="D2" s="54" t="inlineStr">
+      <c r="D2" s="55" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="E2" s="54" t="inlineStr">
+      <c r="E2" s="55" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="F2" s="54" t="inlineStr">
+      <c r="F2" s="55" t="inlineStr">
         <is>
           <t>Cost basis</t>
         </is>
       </c>
-      <c r="G2" s="54" t="inlineStr">
+      <c r="G2" s="55" t="inlineStr">
         <is>
           <t>Yield %</t>
         </is>
       </c>
-      <c r="H2" s="54" t="inlineStr">
+      <c r="H2" s="55" t="inlineStr">
         <is>
           <t>Expected return %</t>
         </is>
       </c>
-      <c r="I2" s="54" t="inlineStr">
+      <c r="I2" s="55" t="inlineStr">
         <is>
           <t>Vol %</t>
         </is>
       </c>
-      <c r="J2" s="54" t="inlineStr">
+      <c r="J2" s="55" t="inlineStr">
         <is>
           <t>As of</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Fidelity 401k</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="54" t="inlineStr">
         <is>
           <t>401k</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="54" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="54" t="inlineStr">
         <is>
           <t>Total market index</t>
         </is>
       </c>
-      <c r="E3" s="56" t="n">
+      <c r="E3" s="57" t="n">
         <v>1400000</v>
       </c>
-      <c r="F3" s="56" t="n">
+      <c r="F3" s="57" t="n">
         <v>900000</v>
       </c>
-      <c r="G3" s="57" t="n"/>
-      <c r="H3" s="57" t="n">
+      <c r="G3" s="58" t="n"/>
+      <c r="H3" s="58" t="n">
         <v>0.08</v>
       </c>
-      <c r="I3" s="57" t="n">
+      <c r="I3" s="58" t="n">
         <v>0.16</v>
       </c>
-      <c r="J3" s="53" t="inlineStr">
+      <c r="J3" s="54" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Fidelity 401k</t>
         </is>
       </c>
-      <c r="B4" s="53" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
         <is>
           <t>401k</t>
         </is>
       </c>
-      <c r="C4" s="53" t="inlineStr">
+      <c r="C4" s="54" t="inlineStr">
         <is>
           <t>Bonds</t>
         </is>
       </c>
-      <c r="D4" s="53" t="inlineStr">
+      <c r="D4" s="54" t="inlineStr">
         <is>
           <t>Bond fund</t>
         </is>
       </c>
-      <c r="E4" s="56" t="n">
+      <c r="E4" s="57" t="n">
         <v>300000</v>
       </c>
-      <c r="F4" s="56" t="n">
+      <c r="F4" s="57" t="n">
         <v>300000</v>
       </c>
-      <c r="G4" s="57" t="n">
+      <c r="G4" s="58" t="n">
         <v>0.03</v>
       </c>
-      <c r="H4" s="57" t="n">
+      <c r="H4" s="58" t="n">
         <v>0.03</v>
       </c>
-      <c r="I4" s="57" t="n">
+      <c r="I4" s="58" t="n">
         <v>0.06</v>
       </c>
-      <c r="J4" s="53" t="inlineStr">
+      <c r="J4" s="54" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Schwab taxable</t>
         </is>
       </c>
-      <c r="B5" s="53" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>Taxable</t>
         </is>
       </c>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="54" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="54" t="inlineStr">
         <is>
           <t>Credit fund</t>
         </is>
       </c>
-      <c r="E5" s="56" t="n">
+      <c r="E5" s="57" t="n">
         <v>500000</v>
       </c>
-      <c r="F5" s="56" t="n">
+      <c r="F5" s="57" t="n">
         <v>480000</v>
       </c>
-      <c r="G5" s="57" t="n">
+      <c r="G5" s="58" t="n">
         <v>0.06</v>
       </c>
-      <c r="H5" s="57" t="n"/>
-      <c r="I5" s="57" t="n"/>
-      <c r="J5" s="53" t="inlineStr">
+      <c r="H5" s="58" t="n"/>
+      <c r="I5" s="58" t="n"/>
+      <c r="J5" s="54" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Equity Trust SDIRA</t>
         </is>
       </c>
-      <c r="B6" s="53" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>SDIRA</t>
         </is>
       </c>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="D6" s="53" t="inlineStr">
+      <c r="D6" s="54" t="inlineStr">
         <is>
           <t>Money market</t>
         </is>
       </c>
-      <c r="E6" s="56" t="n">
+      <c r="E6" s="57" t="n">
         <v>200000</v>
       </c>
-      <c r="F6" s="56" t="n">
+      <c r="F6" s="57" t="n">
         <v>200000</v>
       </c>
-      <c r="G6" s="57" t="n">
+      <c r="G6" s="58" t="n">
         <v>0.045</v>
       </c>
-      <c r="H6" s="57" t="n"/>
-      <c r="I6" s="57" t="n"/>
-      <c r="J6" s="53" t="inlineStr">
+      <c r="H6" s="58" t="n"/>
+      <c r="I6" s="58" t="n"/>
+      <c r="J6" s="54" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>ONE ROW PER ACCOUNT AND SLEEVE, not per ticker. Three index funds in one 401k are one row.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>Account must match the Account column on Positions exactly, or the two cannot be tied together.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>Sleeve: Growth, Income, Bonds or Cash. Anything else is treated as Growth and the app says so.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>Yield, return and vol are optional. Blank means "use the model’s assumption", which it names on screen.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>Do NOT list private deals here. They belong on Positions, and counting them twice would spend the same money twice.</t>
         </is>
@@ -2704,126 +2693,126 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Property  · an asset, a debt, an income stream and a dated event, all at once</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B2" s="54" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="54" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>Mortgage balance</t>
         </is>
       </c>
-      <c r="D2" s="54" t="inlineStr">
+      <c r="D2" s="55" t="inlineStr">
         <is>
           <t>Rate %</t>
         </is>
       </c>
-      <c r="E2" s="54" t="inlineStr">
+      <c r="E2" s="55" t="inlineStr">
         <is>
           <t>Payment / mo</t>
         </is>
       </c>
-      <c r="F2" s="54" t="inlineStr">
+      <c r="F2" s="55" t="inlineStr">
         <is>
           <t>Net rent / mo</t>
         </is>
       </c>
-      <c r="G2" s="54" t="inlineStr">
+      <c r="G2" s="55" t="inlineStr">
         <is>
           <t>Sell in year</t>
         </is>
       </c>
-      <c r="H2" s="54" t="inlineStr">
+      <c r="H2" s="55" t="inlineStr">
         <is>
           <t>Cost to sell %</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Main house</t>
         </is>
       </c>
-      <c r="B3" s="56" t="n">
+      <c r="B3" s="57" t="n">
         <v>1200000</v>
       </c>
-      <c r="C3" s="56" t="n">
+      <c r="C3" s="57" t="n">
         <v>400000</v>
       </c>
-      <c r="D3" s="57" t="n">
+      <c r="D3" s="58" t="n">
         <v>0.035</v>
       </c>
-      <c r="E3" s="56" t="n">
+      <c r="E3" s="57" t="n">
         <v>2600</v>
       </c>
-      <c r="F3" s="56" t="n">
+      <c r="F3" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="53" t="n">
+      <c r="G3" s="54" t="n">
         <v>2050</v>
       </c>
-      <c r="H3" s="57" t="n">
+      <c r="H3" s="58" t="n">
         <v>0.06</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Rental</t>
         </is>
       </c>
-      <c r="B4" s="56" t="n">
+      <c r="B4" s="57" t="n">
         <v>600000</v>
       </c>
-      <c r="C4" s="56" t="n">
+      <c r="C4" s="57" t="n">
         <v>250000</v>
       </c>
-      <c r="D4" s="57" t="n">
+      <c r="D4" s="58" t="n">
         <v>0.05</v>
       </c>
-      <c r="E4" s="56" t="n">
+      <c r="E4" s="57" t="n">
         <v>1600</v>
       </c>
-      <c r="F4" s="56" t="n">
+      <c r="F4" s="57" t="n">
         <v>2200</v>
       </c>
-      <c r="G4" s="53" t="n">
+      <c r="G4" s="54" t="n">
         <v>2055</v>
       </c>
-      <c r="H4" s="57" t="n">
+      <c r="H4" s="58" t="n">
         <v>0.06</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>The sale is counted NET: value, less the cost to sell, less the mortgage still owed.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>Leave Sell in year blank for somewhere you do not plan to sell. It still counts as an asset.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>Cost to sell defaults to 6% if you leave it blank.</t>
         </is>
@@ -2852,99 +2841,99 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Cashflows  · money in or out, year after year</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="B2" s="54" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Amount / yr</t>
         </is>
       </c>
-      <c r="C2" s="54" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>Starts</t>
         </is>
       </c>
-      <c r="D2" s="54" t="inlineStr">
+      <c r="D2" s="55" t="inlineStr">
         <is>
           <t>Ends</t>
         </is>
       </c>
-      <c r="E2" s="54" t="inlineStr">
+      <c r="E2" s="55" t="inlineStr">
         <is>
           <t>Inflates?</t>
         </is>
       </c>
-      <c r="F2" s="54" t="inlineStr">
+      <c r="F2" s="55" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="B3" s="56" t="n">
+      <c r="B3" s="57" t="n">
         <v>60000</v>
       </c>
-      <c r="C3" s="53" t="n">
+      <c r="C3" s="54" t="n">
         <v>2041</v>
       </c>
-      <c r="D3" s="53" t="n">
+      <c r="D3" s="54" t="n">
         <v>2045</v>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" s="53" t="inlineStr">
+      <c r="F3" s="54" t="inlineStr">
         <is>
           <t>Schwab taxable</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Pension</t>
         </is>
       </c>
-      <c r="B4" s="56" t="n">
+      <c r="B4" s="57" t="n">
         <v>24000</v>
       </c>
-      <c r="C4" s="53" t="n">
+      <c r="C4" s="54" t="n">
         <v>2042</v>
       </c>
-      <c r="D4" s="53" t="n"/>
-      <c r="E4" s="53" t="inlineStr">
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F4" s="53" t="inlineStr"/>
+      <c r="F4" s="54" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>LEAVE Ends BLANK for something that runs for the rest of the plan, like a pension.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>Negative amounts are money going out.</t>
         </is>
@@ -2971,68 +2960,68 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Events  · the one-offs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="B2" s="54" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C2" s="54" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D2" s="54" t="inlineStr">
+      <c r="D2" s="55" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Inheritance</t>
         </is>
       </c>
-      <c r="B3" s="53" t="n">
+      <c r="B3" s="54" t="n">
         <v>2047</v>
       </c>
-      <c r="C3" s="58" t="n">
+      <c r="C3" s="59" t="n">
         <v>300000</v>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="54" t="inlineStr">
         <is>
           <t>Schwab taxable</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>New roof</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n">
+      <c r="B4" s="54" t="n">
         <v>2043</v>
       </c>
-      <c r="C4" s="58" t="n">
+      <c r="C4" s="59" t="n">
         <v>-45000</v>
       </c>
-      <c r="D4" s="53" t="inlineStr"/>
+      <c r="D4" s="54" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>POSITIVE is money arriving, NEGATIVE is money going out. A bill raises what that year needs.</t>
         </is>
